--- a/backend/plantilla/kdd-portal-sheets.xlsx
+++ b/backend/plantilla/kdd-portal-sheets.xlsx
@@ -112,7 +112,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -124,6 +124,8 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -620,7 +622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -628,6 +630,7 @@
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -656,6 +659,11 @@
           <t>CalendarId</t>
         </is>
       </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Icono</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -679,6 +687,11 @@
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr"/>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>💱</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -694,6 +707,7 @@
       <c r="C3" s="7" t="inlineStr"/>
       <c r="D3" s="7" t="inlineStr"/>
       <c r="E3" s="7" t="inlineStr"/>
+      <c r="F3" s="10" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -709,6 +723,7 @@
       <c r="C4" s="7" t="inlineStr"/>
       <c r="D4" s="7" t="inlineStr"/>
       <c r="E4" s="7" t="inlineStr"/>
+      <c r="F4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -724,11 +739,12 @@
       <c r="C5" s="7" t="inlineStr"/>
       <c r="D5" s="7" t="inlineStr"/>
       <c r="E5" s="7" t="inlineStr"/>
+      <c r="F5" s="10" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>⚠️ Los TeamId deben coincidir con los ids de TEAMS en media/main.js. Filas grises: rellenar al incorporar cada equipo.</t>
+          <t>⚠️ Añadir un equipo = añadir una fila (la extensión los lee de aquí). TeamId sin espacios. Icono (emoji) opcional. Filas grises: rellenar al incorporar cada equipo.</t>
         </is>
       </c>
     </row>
